--- a/QAlegend/src/main/resources/TestData.xlsx
+++ b/QAlegend/src/main/resources/TestData.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\git\QALegend\QAlegend\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F76E20-3D7D-4DFA-AA47-C7537B642C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB597BA-CF74-4DA5-9DF6-D98D14079938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" activeTab="2" xr2:uid="{D6354474-DDE8-40C4-9A15-4505DE7CE4F6}"/>
+    <workbookView xWindow="32205" yWindow="1380" windowWidth="17280" windowHeight="8880" xr2:uid="{98EF1B6F-D532-4A49-B6C5-F9CE3590C94A}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginPage" sheetId="1" r:id="rId1"/>
     <sheet name="ResetPage" sheetId="2" r:id="rId2"/>
     <sheet name="HomePage" sheetId="3" r:id="rId3"/>
+    <sheet name="RolesPage" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,24 +28,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
   <si>
     <t>admin</t>
+  </si>
+  <si>
+    <t>The email must be a valid email address.</t>
+  </si>
+  <si>
+    <t>Retailer</t>
   </si>
   <si>
     <t>These credentials do not match our records.</t>
   </si>
   <si>
-    <t>The email must be a valid email address.</t>
-  </si>
-  <si>
-    <t>Reset Password - Demo POS</t>
-  </si>
-  <si>
-    <t>We can't find a user with that e-mail address.</t>
-  </si>
-  <si>
-    <t>https://qalegend.com/billing/public/home</t>
+    <t>https://qalegend.com/billing/public/password/reset</t>
   </si>
 </sst>
 </file>
@@ -406,13 +404,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29F2BE2E-0915-466B-AF05-5C2F05D4E23F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7731B588-BC5E-4FAF-B43D-A56DA437313B}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="28.21875" customWidth="1"/>
-    <col min="2" max="2" width="17.77734375" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -424,7 +418,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -438,50 +432,51 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A4BF396-AE55-4087-9484-12A9E65BB625}">
-  <dimension ref="A1:A3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC4C1285-316D-4FB1-9686-ABA8DA9F68A6}">
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="41.5546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D81AF106-10E1-4D43-8086-D026AB738160}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="36.88671875" customWidth="1"/>
+    <col min="1" max="1" width="52.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1" xr:uid="{443FC8EE-BCC5-4DB8-BE08-A9AAA811597D}"/>
+    <hyperlink ref="A1" r:id="rId1" xr:uid="{1E52584B-C399-4F2E-B550-D66EECCA5C24}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FA8833A-A200-419C-853A-A269A3016550}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63E7AF09-1A2F-4371-AFA8-C534C0C10D0D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/QAlegend/src/main/resources/TestData.xlsx
+++ b/QAlegend/src/main/resources/TestData.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\git\QALegend\QAlegend\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB597BA-CF74-4DA5-9DF6-D98D14079938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08AEA450-F144-4C3E-8D72-ADB6B22C7BCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32205" yWindow="1380" windowWidth="17280" windowHeight="8880" xr2:uid="{98EF1B6F-D532-4A49-B6C5-F9CE3590C94A}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8880" activeTab="3" xr2:uid="{98EF1B6F-D532-4A49-B6C5-F9CE3590C94A}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginPage" sheetId="1" r:id="rId1"/>
     <sheet name="ResetPage" sheetId="2" r:id="rId2"/>
-    <sheet name="HomePage" sheetId="3" r:id="rId3"/>
-    <sheet name="RolesPage" sheetId="4" r:id="rId4"/>
+    <sheet name="UsersPage" sheetId="3" r:id="rId3"/>
+    <sheet name="HomePage" sheetId="5" r:id="rId4"/>
+    <sheet name="RolesPage" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>admin</t>
   </si>
@@ -42,7 +43,16 @@
     <t>These credentials do not match our records.</t>
   </si>
   <si>
-    <t>https://qalegend.com/billing/public/password/reset</t>
+    <t>Reset Password - Demo POS</t>
+  </si>
+  <si>
+    <t>We can't find a user with that e-mail address.</t>
+  </si>
+  <si>
+    <t>testuser@qalegend.com</t>
+  </si>
+  <si>
+    <t>Home - Maxfest Enterprises PVT LTD,Kochi</t>
   </si>
 </sst>
 </file>
@@ -407,6 +417,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7731B588-BC5E-4FAF-B43D-A56DA437313B}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -433,7 +446,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC4C1285-316D-4FB1-9686-ABA8DA9F68A6}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="52.109375" customWidth="1"/>
@@ -449,9 +462,14 @@
         <v>1</v>
       </c>
     </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1" xr:uid="{1E52584B-C399-4F2E-B550-D66EECCA5C24}"/>
+    <hyperlink ref="A1" r:id="rId1" display="https://qalegend.com/billing/public/password/reset" xr:uid="{1E52584B-C399-4F2E-B550-D66EECCA5C24}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -461,12 +479,39 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FA8833A-A200-419C-853A-A269A3016550}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="23.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" r:id="rId1" xr:uid="{C877541E-8993-408D-807C-385B0EF31621}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A31C8702-DEF6-4B20-A185-DB3DD61ADD62}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63E7AF09-1A2F-4371-AFA8-C534C0C10D0D}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
